--- a/发送映射模板.xlsx
+++ b/发送映射模板.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>微信昵称</t>
+          <t>微信备注名/昵称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>1. 第一列填文件名关键词，第二列填微信昵称（与微信显示一致）</t>
+          <t>1. 第一列填文件名关键词，第二列填对方的微信备注名（优先）或昵称</t>
         </is>
       </c>
     </row>
@@ -585,14 +585,21 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>4. 第一行为表头，程序自动跳过</t>
+          <t>4. 多个关键词映射到同一个人时会自动合并去重，只发送一次</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>5. 请确保微信PC版已登录，昵称/备注名与微信一致</t>
+          <t>5. 第一行为表头，程序自动跳过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>6. 请确保微信PC版已登录；重名时建议填微信号（唯一）</t>
         </is>
       </c>
     </row>
